--- a/AAII_Financials/Quarterly/LNSTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNSTY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
   <si>
     <t>LNSTY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,59 +656,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,8 +743,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -765,8 +778,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -794,8 +813,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,8 +832,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -836,8 +863,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,8 +898,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -894,8 +933,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -923,8 +968,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,8 +984,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -962,8 +1015,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -991,8 +1050,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1004,8 +1069,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1033,8 +1100,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1062,8 +1135,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1091,8 +1170,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1120,8 +1205,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1149,8 +1240,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1178,8 +1275,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1207,8 +1310,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1236,8 +1345,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1265,8 +1380,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,8 +1415,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1323,8 +1450,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1352,8 +1485,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1381,8 +1520,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1410,8 +1555,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1439,8 +1590,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1468,42 +1625,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1515,8 +1684,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1528,37 +1699,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4350400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4657600</v>
+      </c>
+      <c r="F41" s="3">
         <v>4620400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4617400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4560000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4368700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4447800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4330000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3866500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3575800</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1581,42 +1760,54 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>272300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>251800</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2550200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2730200</v>
+      </c>
+      <c r="F43" s="3">
         <v>3294700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3292600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2864700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2744500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2774100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2700700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1990500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1840800</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1644,153 +1835,189 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>866995500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>928200000</v>
+      </c>
+      <c r="F45" s="3">
         <v>952937700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>952323900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>972614300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>931808800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1023355900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>996250200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>954864800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>883066100</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>873896100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>935587700</v>
+      </c>
+      <c r="F46" s="3">
         <v>960852800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>960233900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>980331900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>939202600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1030577800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1003280900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>961251900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>888973000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>89800</v>
+      </c>
+      <c r="F47" s="3">
         <v>571200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>570900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>509500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>488100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>517200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>503500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>515700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>476900</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>852600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>912700</v>
+      </c>
+      <c r="F48" s="3">
         <v>885900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>885300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>912000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>873700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>979800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>953800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>960300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>888100</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41276000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>44189800</v>
+      </c>
+      <c r="F49" s="3">
         <v>41375300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>41348600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>42221200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>40449800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>42956600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>41818800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>42250700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>39073800</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1818,8 +2045,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1847,37 +2080,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>536100</v>
+      </c>
+      <c r="F52" s="3">
         <v>539600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>539300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>486600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>466200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>481600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>468900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>444600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>411200</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1905,37 +2150,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>917434300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>982199400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1005080400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1004433000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1025385900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>982366400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1076287000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1047779300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1006272700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>930608500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1947,8 +2204,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1960,182 +2219,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2359900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2526500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1995500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1994200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>328600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>314800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1922700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1871800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>497600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>460200</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1993100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2133800</v>
+      </c>
+      <c r="F58" s="3">
         <v>3639700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3637400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2835400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2716400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3559500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3465200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1738700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1607900</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>867656500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>928907700</v>
+      </c>
+      <c r="F59" s="3">
         <v>953979000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>953364600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>974314700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>933437900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1024450100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>997315400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>956067200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>884178200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>872009500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>933567900</v>
+      </c>
+      <c r="F60" s="3">
         <v>959734400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>959116200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>978980500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>937907900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1029932300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1002652400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>959659000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>887499900</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10561200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>11306800</v>
+      </c>
+      <c r="F61" s="3">
         <v>10169700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>10163200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>9623200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9219500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>8678200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>8448400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>9007800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8330500</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>711100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>761300</v>
+      </c>
+      <c r="F62" s="3">
         <v>731700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>731300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>817800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>783400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>865400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>842500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>851900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>787800</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2163,8 +2460,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2192,8 +2495,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2221,37 +2530,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>885944600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>948486800</v>
+      </c>
+      <c r="F66" s="3">
         <v>973450300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>972823300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>992339600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>950706600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1042370800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1014761500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>972353800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>899240100</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2263,8 +2584,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2292,8 +2615,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2321,8 +2650,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2350,8 +2685,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2379,37 +2720,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2352400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2518400</v>
+      </c>
+      <c r="F72" s="3">
         <v>2407500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2406000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3715500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3559700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4483400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4364600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4626800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4278900</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2437,8 +2790,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2466,8 +2825,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2495,37 +2860,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28810500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>30844400</v>
+      </c>
+      <c r="F76" s="3">
         <v>28798000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>28779500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>30324300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>29052100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>31220900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>30393900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>31322400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>28967200</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2553,42 +2930,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2616,8 +3005,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2629,37 +3024,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>62800</v>
+      </c>
+      <c r="F83" s="3">
         <v>87700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>85400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>58400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>54000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>93600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>101200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>77200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2687,8 +3090,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2716,8 +3125,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2745,8 +3160,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2774,8 +3195,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2803,37 +3230,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1339600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1434100</v>
+      </c>
+      <c r="F89" s="3">
         <v>793700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>793100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1170600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1121500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>701500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>682900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1015700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>939300</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,37 +3284,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-24600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-24600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-56700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-54300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-21000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-20400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-50000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-46200</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2903,8 +3350,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2932,37 +3385,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-457000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-489200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-346900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-346700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-402500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-385600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-468300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-455900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-107800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-99700</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2974,37 +3439,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>136500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>146100</v>
+      </c>
+      <c r="F96" s="3">
         <v>267900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>267800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>124800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>119600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>263700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>256700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>106600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>98600</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3032,8 +3505,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3061,8 +3540,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3090,91 +3575,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-974600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1043400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-383600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-383300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-712700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-682800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>20400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-528900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-489200</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-69300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-67400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>36100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>33400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>75300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>81500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-113300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-121300</v>
+      </c>
+      <c r="F102" s="3">
         <v>48000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>48000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>51000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>48800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>184900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>180000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>415100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>383900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LNSTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNSTY_QTR_FIN.xlsx
@@ -1777,10 +1777,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2550200</v>
+        <v>2215900</v>
       </c>
       <c r="E43" s="3">
-        <v>2730200</v>
+        <v>2372300</v>
       </c>
       <c r="F43" s="3">
         <v>3294700</v>
@@ -1847,10 +1847,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>866995500</v>
+        <v>867056800</v>
       </c>
       <c r="E45" s="3">
-        <v>928200000</v>
+        <v>928265600</v>
       </c>
       <c r="F45" s="3">
         <v>952937700</v>
@@ -2092,10 +2092,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>500800</v>
+        <v>414400</v>
       </c>
       <c r="E52" s="3">
-        <v>536100</v>
+        <v>443600</v>
       </c>
       <c r="F52" s="3">
         <v>539600</v>
@@ -2227,10 +2227,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2359900</v>
+        <v>404400</v>
       </c>
       <c r="E57" s="3">
-        <v>2526500</v>
+        <v>432900</v>
       </c>
       <c r="F57" s="3">
         <v>1995500</v>
@@ -2262,10 +2262,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1993100</v>
+        <v>2010600</v>
       </c>
       <c r="E58" s="3">
-        <v>2133800</v>
+        <v>2152500</v>
       </c>
       <c r="F58" s="3">
         <v>3639700</v>
@@ -2297,10 +2297,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>867656500</v>
+        <v>868007100</v>
       </c>
       <c r="E59" s="3">
-        <v>928907700</v>
+        <v>929282900</v>
       </c>
       <c r="F59" s="3">
         <v>953979000</v>
@@ -3032,10 +3032,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>65600</v>
+        <v>80200</v>
       </c>
       <c r="E83" s="3">
-        <v>62800</v>
+        <v>76900</v>
       </c>
       <c r="F83" s="3">
         <v>87700</v>

--- a/AAII_Financials/Quarterly/LNSTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNSTY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>LNSTY</t>
   </si>
@@ -656,66 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -749,8 +756,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -784,8 +797,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -819,8 +838,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -834,8 +859,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -869,8 +896,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -904,8 +937,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -939,8 +978,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -974,8 +1019,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -986,8 +1037,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1021,8 +1074,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1056,8 +1115,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1071,8 +1136,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1106,8 +1173,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1141,8 +1214,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1176,8 +1255,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1211,8 +1296,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1246,8 +1337,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1281,8 +1378,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1316,8 +1419,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1351,8 +1460,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1386,8 +1501,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1421,8 +1542,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1456,8 +1583,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1491,8 +1624,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1526,8 +1665,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1561,8 +1706,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1596,8 +1747,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1631,48 +1788,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1686,8 +1855,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1701,51 +1872,59 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4729400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4460000</v>
+      </c>
+      <c r="F41" s="3">
         <v>4350400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4657600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4620400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4617400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4560000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4368700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4447800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4330000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3866500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3575800</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>290500</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>273900</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1766,48 +1945,60 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>272300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>251800</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3234700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3050400</v>
+      </c>
+      <c r="F43" s="3">
         <v>2215900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2372300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3294700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3292600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2864700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2744500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2774100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2700700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1990500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1840800</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1841,183 +2032,219 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1059268400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>998927600</v>
+      </c>
+      <c r="F45" s="3">
         <v>867056800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>928265600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>952937700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>952323900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>972614300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>931808800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1023355900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>996250200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>954864800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>883066100</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1067881900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1007050500</v>
+      </c>
+      <c r="F46" s="3">
         <v>873896100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>935587700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>960852800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>960233900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>980331900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>939202600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1030577800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1003280900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>961251900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>888973000</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>98200</v>
+      </c>
+      <c r="F47" s="3">
         <v>83900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>89800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>571200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>570900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>509500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>488100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>517200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>503500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>515700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>476900</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>789100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>744200</v>
+      </c>
+      <c r="F48" s="3">
         <v>852600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>912700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>885900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>885300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>912000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>873700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>979800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>953800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>960300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>888100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41359100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>39003100</v>
+      </c>
+      <c r="F49" s="3">
         <v>41276000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>44189800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>41375300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>41348600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>42221200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>40449800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>42956600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>41818800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>42250700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>39073800</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2051,8 +2278,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,43 +2319,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>752200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>709300</v>
+      </c>
+      <c r="F52" s="3">
         <v>414400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>443600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>539600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>539300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>486600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>466200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>481600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>468900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>444600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>411200</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2156,43 +2401,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1111756400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1048425700</v>
+      </c>
+      <c r="F54" s="3">
         <v>917434300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>982199400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1005080400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1004433000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1025385900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>982366400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1076287000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1047779300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1006272700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>930608500</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2206,8 +2463,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2221,218 +2480,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2246900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2118900</v>
+      </c>
+      <c r="F57" s="3">
         <v>404400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>432900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1995500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1994200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>328600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>314800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1922700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1871800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>497600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>460200</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3429200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3233900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2010600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2152500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3639700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3637400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2835400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2716400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3559500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3465200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1738700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1607900</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1060383600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>999979300</v>
+      </c>
+      <c r="F59" s="3">
         <v>868007100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>929282900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>953979000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>953364600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>974314700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>933437900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1024450100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>997315400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>956067200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>884178200</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1066273500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1005533700</v>
+      </c>
+      <c r="F60" s="3">
         <v>872009500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>933567900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>959734400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>959116200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>978980500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>937907900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1029932300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1002652400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>959659000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>887499900</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10302800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9715900</v>
+      </c>
+      <c r="F61" s="3">
         <v>10561200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11306800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>10169700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10163200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9623200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9219500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8678200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8448400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9007800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8330500</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>700100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>660200</v>
+      </c>
+      <c r="F62" s="3">
         <v>711100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>761300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>731700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>731300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>817800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>783400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>865400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>842500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>851900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>787800</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2466,8 +2763,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,8 +2804,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2536,43 +2845,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1079942500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1018424000</v>
+      </c>
+      <c r="F66" s="3">
         <v>885944600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>948486800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>973450300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>972823300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>992339600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>950706600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1042370800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1014761500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>972353800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>899240100</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2586,8 +2907,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2621,8 +2944,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2656,8 +2985,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2691,8 +3026,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2726,43 +3067,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2193500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2068500</v>
+      </c>
+      <c r="F72" s="3">
         <v>2352400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2518400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2407500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2406000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3715500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3559700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4483400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4364600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4626800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4278900</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2796,8 +3149,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2831,8 +3190,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2866,43 +3231,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28972500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>27322100</v>
+      </c>
+      <c r="F76" s="3">
         <v>28810500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>30844400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>28798000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>28779500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>30324300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>29052100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>31220900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>30393900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>31322400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>28967200</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2936,48 +3313,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3011,8 +3400,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3026,43 +3421,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>83400</v>
+      </c>
+      <c r="F83" s="3">
         <v>80200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>76900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>87700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>85400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>58400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>54000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>93600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>101200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>77200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3096,8 +3499,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3131,8 +3540,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3166,8 +3581,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3201,8 +3622,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3236,43 +3663,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1015200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>957400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1339600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1434100</v>
       </c>
-      <c r="F89" s="3">
-        <v>793700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>793100</v>
-      </c>
       <c r="H89" s="3">
+        <v>774100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>773600</v>
+      </c>
+      <c r="J89" s="3">
         <v>1170600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1121500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>701500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>682900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1015700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>939300</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3286,43 +3725,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-21900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-23500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-24600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-24600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-56700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-54300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-21000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-20400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-50000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-46200</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3356,8 +3803,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3391,43 +3844,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-461700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-435400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-457000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-489200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-346900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-346700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-402500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-385600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-468300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-455900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-107800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-99700</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3441,43 +3906,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>322600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>304300</v>
+      </c>
+      <c r="F96" s="3">
         <v>136500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>146100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>267900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>267800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>124800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>119600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>263700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>256700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>106600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>98600</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3511,8 +3984,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3546,8 +4025,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3581,109 +4066,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-518600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-489000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-974600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1043400</v>
       </c>
-      <c r="F100" s="3">
-        <v>-383600</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-383300</v>
-      </c>
       <c r="H100" s="3">
+        <v>-364000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-363700</v>
+      </c>
+      <c r="J100" s="3">
         <v>-712700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-682800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>21000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>20400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-528900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-489200</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-4500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-4300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-69300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-67400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>36100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>33400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>75300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>81500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-113300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-121300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>48000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>48000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>51000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>48800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>184900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>180000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>415100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>383900</v>
       </c>
     </row>
